--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_186_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_186_R19.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1013</v>
+        <v>2.2301</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7088</v>
+        <v>3.7703</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6075</v>
+        <v>-1.5402</v>
       </c>
       <c r="G2" t="n">
         <v>1.915</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9735</v>
+        <v>0.1553</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7468</v>
+        <v>0.3148</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2267</v>
+        <v>-0.1595</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.303</v>
+        <v>1.3138</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0207</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3237</v>
+        <v>0.3909</v>
       </c>
       <c r="G3" t="n">
         <v>1.5135</v>
@@ -688,13 +688,13 @@
         <v>0.232</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0482</v>
+        <v>-0.0373</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7468</v>
+        <v>0.1968</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3014</v>
+        <v>-0.2341</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3943</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1081</v>
+        <v>0.2596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0325</v>
+        <v>0.1505</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0755</v>
+        <v>0.1091</v>
       </c>
       <c r="G4" t="n">
         <v>0.2429</v>
@@ -766,13 +766,13 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3668</v>
+        <v>-0.2153</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2921</v>
+        <v>-0.2585</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4794</v>
+        <v>-0.8087</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2201</v>
+        <v>-0.3813</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2594</v>
+        <v>-0.4274</v>
       </c>
       <c r="G5" t="n">
         <v>0.8621</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8905</v>
+        <v>0.5612</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2636</v>
+        <v>0.1024</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6269</v>
+        <v>0.4589</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6679</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3587</v>
+        <v>2.3359</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.0266</v>
+        <v>-3.156</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.8704</v>
+        <v>-0.8072</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2065</v>
+        <v>0.1129</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.6639</v>
+        <v>-0.9201</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9424</v>
+        <v>2.4665</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2261</v>
+        <v>0.8605</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7163</v>
+        <v>1.606</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.9281</v>
+        <v>-3.2738</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9804</v>
+        <v>-0.7477</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.9477</v>
+        <v>-2.5261</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3776</v>
+        <v>-0.3892</v>
       </c>
       <c r="T6" t="n">
-        <v>1.172</v>
+        <v>-0.0431</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2056</v>
+        <v>-0.3462</v>
       </c>
       <c r="V6" t="n">
-        <v>4.2888</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>4.2888</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7249</v>
+        <v>-1.3243</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6599</v>
+        <v>-1.2929</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.065</v>
+        <v>-0.0314</v>
       </c>
       <c r="G7" t="n">
         <v>0.2725</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0565</v>
+        <v>0.4571</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1641</v>
+        <v>0.5311</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1076</v>
+        <v>-0.074</v>
       </c>
       <c r="V7" t="n">
         <v>0.9615</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1575</v>
+        <v>-1.3772</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8641</v>
+        <v>1.9183</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0216</v>
+        <v>-3.2955</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8072</v>
+        <v>-5.8704</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1129</v>
+        <v>-2.2065</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9201</v>
+        <v>-3.6639</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4665</v>
+        <v>-1.9424</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8605</v>
+        <v>-1.2261</v>
       </c>
       <c r="L8" t="n">
-        <v>1.606</v>
+        <v>-0.7163</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.2738</v>
+        <v>-3.9281</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7477</v>
+        <v>-0.9804</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.5261</v>
+        <v>-2.9477</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7266</v>
+        <v>0.6684</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5149</v>
+        <v>0.7316</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2117</v>
+        <v>-0.0633</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0722</v>
+        <v>4.2888</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>4.2888</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1865</v>
+        <v>-2.1443</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8144</v>
+        <v>2.3598</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3721</v>
+        <v>-4.5041</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.9249</v>
+        <v>1.1931</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9604</v>
+        <v>3.6324</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9645</v>
+        <v>-2.4393</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9736</v>
+        <v>2.7157</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6953</v>
+        <v>3.4688</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2783</v>
+        <v>-0.7531</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9513</v>
+        <v>-1.5226</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2651</v>
+        <v>0.1636</v>
       </c>
       <c r="O9" t="n">
         <v>-1.6862</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1275</v>
+        <v>0.3431</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4065</v>
+        <v>0.2677</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2789</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4665</v>
+        <v>-3.2166</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3943</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1867</v>
+        <v>-2.6937</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.4896</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8808</v>
+        <v>-3.1833</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1811</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9764</v>
+        <v>1.4695</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6122</v>
+        <v>1.4077</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3642</v>
+        <v>0.0617</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2862</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4782</v>
+        <v>-3.1098</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3284</v>
+        <v>0.3525</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.8066</v>
+        <v>-3.4622</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1931</v>
+        <v>-1.497</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6324</v>
+        <v>-1.9855</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4393</v>
+        <v>0.4885</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7157</v>
+        <v>0.5332</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4688</v>
+        <v>-1.2702</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7531</v>
+        <v>1.8034</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5226</v>
+        <v>-2.0303</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1636</v>
+        <v>-0.7153</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6862</v>
+        <v>-1.3149</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0092</v>
+        <v>-0.5406</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2363</v>
+        <v>-0.1808</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2271</v>
+        <v>-0.3598</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.2166</v>
+        <v>-1.0722</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.7527</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2949</v>
+        <v>-3.9729</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2345</v>
+        <v>-2.7017</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5294</v>
+        <v>-1.2712</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.497</v>
+        <v>-3.9249</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9855</v>
+        <v>-0.9604</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4885</v>
+        <v>-2.9645</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5332</v>
+        <v>-1.9736</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2702</v>
+        <v>-0.6953</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8034</v>
+        <v>-1.2783</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0303</v>
+        <v>-1.9513</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7153</v>
+        <v>-0.2651</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3149</v>
+        <v>-1.6862</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7257</v>
+        <v>0.3411</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2987</v>
+        <v>0.5192</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.427</v>
+        <v>-0.1781</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0722</v>
+        <v>1.4665</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.2657</v>
+        <v>-5.7352</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.494</v>
+        <v>-2.1651</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7717</v>
+        <v>-3.5701</v>
       </c>
       <c r="G13" t="n">
         <v>-7.1585</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1589</v>
+        <v>0.3716</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.187</v>
+        <v>0.1419</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0281</v>
+        <v>0.2298</v>
       </c>
       <c r="V13" t="n">
         <v>0.8197</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.9293</v>
+        <v>-18.1827</v>
       </c>
       <c r="E14" t="n">
-        <v>5.012</v>
+        <v>5.758799999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-23.9415</v>
+        <v>-23.9414</v>
       </c>
       <c r="G14" t="n">
         <v>-14.44</v>
@@ -1522,7 +1522,7 @@
         <v>3.7536</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8644</v>
+        <v>1.864400000000001</v>
       </c>
       <c r="L14" t="n">
         <v>1.8891</v>
@@ -1546,16 +1546,16 @@
         <v>4.6393</v>
       </c>
       <c r="S14" t="n">
-        <v>2.438</v>
+        <v>3.1849</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2858</v>
+        <v>4.0326</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8476999999999999</v>
+        <v>-0.8478000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.03109999999999935</v>
+        <v>0.03109999999999979</v>
       </c>
       <c r="W14" t="n">
         <v>9.5701</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1374</v>
+        <v>5.7658</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9029</v>
+        <v>5.1388</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2345</v>
+        <v>0.627</v>
       </c>
       <c r="G15" t="n">
         <v>4.9475</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.72</v>
+        <v>-0.0916</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0272</v>
+        <v>0.2087</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6928</v>
+        <v>-0.3002</v>
       </c>
       <c r="V15" t="n">
         <v>0.6778999999999999</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0649</v>
+        <v>4.4674</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8605</v>
+        <v>4.8644</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2044</v>
+        <v>-0.397</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5964</v>
+        <v>4.4875</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7696</v>
+        <v>2.6974</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8268</v>
+        <v>1.7901</v>
       </c>
       <c r="J16" t="n">
-        <v>3.607</v>
+        <v>4.7591</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5629</v>
+        <v>2.4906</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0441</v>
+        <v>2.2685</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0106</v>
+        <v>-0.2716</v>
       </c>
       <c r="N16" t="n">
         <v>0.2067</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2173</v>
+        <v>-0.4783</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1757</v>
+        <v>0.1217</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8883</v>
+        <v>0.1928</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7126</v>
+        <v>-0.0712</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4254</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0057</v>
+        <v>4.0498</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1567</v>
+        <v>3.4503</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.151</v>
+        <v>0.5995</v>
       </c>
       <c r="G17" t="n">
-        <v>4.4875</v>
+        <v>3.5964</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6974</v>
+        <v>1.7696</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7901</v>
+        <v>1.8268</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7591</v>
+        <v>3.607</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4906</v>
+        <v>1.5629</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2685</v>
+        <v>2.0441</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2716</v>
+        <v>-0.0106</v>
       </c>
       <c r="N17" t="n">
         <v>0.2067</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4783</v>
+        <v>-0.2173</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.34</v>
+        <v>-0.1909</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5149</v>
+        <v>-0.2985</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1749</v>
+        <v>0.1076</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.214</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5381</v>
+        <v>2.2417</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5668</v>
+        <v>3.8056</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0286</v>
+        <v>-1.5639</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0542</v>
+        <v>0.681</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4946</v>
+        <v>1.1126</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5488</v>
+        <v>-0.4316</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2582</v>
+        <v>2.8079</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0742</v>
+        <v>2.3429</v>
       </c>
       <c r="L19" t="n">
-        <v>0.184</v>
+        <v>0.465</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.204</v>
+        <v>-2.1269</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5688</v>
+        <v>-1.2303</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3648</v>
+        <v>-0.8966</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7159</v>
+        <v>-0.4393</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3239</v>
+        <v>-0.0745</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.608</v>
+        <v>-0.3648</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7528</v>
+        <v>1.1407</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2159</v>
+        <v>1.6713</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4631</v>
+        <v>-0.5306</v>
       </c>
       <c r="G20" t="n">
-        <v>0.681</v>
+        <v>2.3045</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1126</v>
+        <v>0.8824</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4316</v>
+        <v>1.4221</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8079</v>
+        <v>1.84</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3429</v>
+        <v>1.462</v>
       </c>
       <c r="L20" t="n">
-        <v>0.465</v>
+        <v>0.378</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1269</v>
+        <v>0.4645</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2303</v>
+        <v>-0.5796</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8966</v>
+        <v>1.0441</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9282</v>
+        <v>-0.2693</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6642</v>
+        <v>-0.1687</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.264</v>
+        <v>-0.1006</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0722</v>
+        <v>-2.2862</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9391</v>
+        <v>0.954</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6713</v>
+        <v>1.9154</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7322</v>
+        <v>-0.9614</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3045</v>
+        <v>0.0542</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8824</v>
+        <v>-0.4946</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4221</v>
+        <v>0.5488</v>
       </c>
       <c r="J21" t="n">
-        <v>1.84</v>
+        <v>0.2582</v>
       </c>
       <c r="K21" t="n">
-        <v>1.462</v>
+        <v>0.0742</v>
       </c>
       <c r="L21" t="n">
-        <v>0.378</v>
+        <v>0.184</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4645</v>
+        <v>-0.204</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5796</v>
+        <v>-0.5688</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0441</v>
+        <v>0.3648</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4709</v>
+        <v>0.1318</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1687</v>
+        <v>0.6726</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3022</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2862</v>
+        <v>0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2862</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3247</v>
+        <v>0.4985</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5594</v>
+        <v>2.4415</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2347</v>
+        <v>-1.943</v>
       </c>
       <c r="G22" t="n">
         <v>-0.394</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2548</v>
+        <v>0.4285</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.4602</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3233</v>
+        <v>-0.0316</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2887</v>
+        <v>0.1587</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0679</v>
+        <v>-0.5218</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2208</v>
+        <v>0.6805</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1607</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4784</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6844</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1628</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9624</v>
+        <v>-3.4012</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5189</v>
+        <v>-2.283</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4435</v>
+        <v>-1.1182</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1545</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5759</v>
+        <v>-0.0147</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2161</v>
+        <v>0.0198</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3598</v>
+        <v>-0.0345</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.9295</v>
+        <v>19.7159</v>
       </c>
       <c r="E25" t="n">
         <v>23.4054</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.475899999999999</v>
+        <v>-3.6896</v>
       </c>
       <c r="G25" t="n">
         <v>14.4401</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6286</v>
+        <v>2.628599999999999</v>
       </c>
       <c r="I25" t="n">
         <v>11.8115</v>
@@ -2404,13 +2404,13 @@
         <v>11.5976</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.438</v>
+        <v>-1.6518</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8477999999999999</v>
+        <v>0.8479000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.2858</v>
+        <v>-2.4996</v>
       </c>
       <c r="V25" t="n">
         <v>-0.03110000000000002</v>
@@ -2419,7 +2419,7 @@
         <v>9.003</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.034099999999999</v>
+        <v>-9.0341</v>
       </c>
     </row>
   </sheetData>
